--- a/uploads/valid_data.xlsx
+++ b/uploads/valid_data.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Valid data" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>TEL CLIENT</t>
   </si>
@@ -26,12 +26,6 @@
   </si>
   <si>
     <t>0661250473</t>
-  </si>
-  <si>
-    <t>0611250473</t>
-  </si>
-  <si>
-    <t>0611111111</t>
   </si>
 </sst>
 </file>
@@ -385,58 +379,4 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
-</file>
-
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>2802966</v>
-      </c>
-      <c r="C2">
-        <v>50946</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>123</v>
-      </c>
-      <c r="C3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>999</v>
-      </c>
-      <c r="C4">
-        <v>999</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>